--- a/Result/profitability/1234.xlsx
+++ b/Result/profitability/1234.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.06</v>
       </c>
       <c r="M2" t="n">
-        <v>0.45625</v>
+        <v>0.38125</v>
       </c>
       <c r="N2" t="n">
-        <v>28.685</v>
+        <v>28.32875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.355</v>
+        <v>0.345</v>
       </c>
       <c r="N3" t="n">
-        <v>28.53625</v>
+        <v>28.9575</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.21</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3325</v>
+        <v>0.295</v>
       </c>
       <c r="N4" t="n">
-        <v>29.39</v>
+        <v>30.30875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2575</v>
+        <v>0.2525</v>
       </c>
       <c r="N5" t="n">
-        <v>29.435</v>
+        <v>29.62</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.11</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2275</v>
+        <v>0.19</v>
       </c>
       <c r="N6" t="n">
-        <v>29.40875</v>
+        <v>29.17375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.11</v>
       </c>
       <c r="M7" t="n">
-        <v>0.165</v>
+        <v>0.15</v>
       </c>
       <c r="N7" t="n">
-        <v>29.54625</v>
+        <v>29.72375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.37</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1575</v>
+        <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>30.555</v>
+        <v>31.43625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2108</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1455</v>
+      </c>
+      <c r="E75" t="n">
+        <v>654</v>
+      </c>
+      <c r="F75" t="n">
+        <v>31</v>
+      </c>
+      <c r="G75" t="n">
+        <v>63</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.00%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>97</v>
+      </c>
+      <c r="J75" t="n">
+        <v>160</v>
+      </c>
+      <c r="K75" t="n">
+        <v>125</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.4875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>29.0075</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.06896551724137945</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>7.050000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2943632567849688</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.03999999999999998</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.1142857142857142</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.05013550135501355</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
